--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120165973</v>
+        <v>120165975</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R2" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120165974</v>
+        <v>120165973</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120159863</v>
+        <v>120165974</v>
       </c>
       <c r="B4" t="n">
-        <v>91832</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R4" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120165975</v>
+        <v>120159863</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661173</v>
+        <v>661167</v>
       </c>
       <c r="R5" t="n">
-        <v>7187968</v>
+        <v>7188060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120165975</v>
+        <v>120165974</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661173</v>
+        <v>660916</v>
       </c>
       <c r="R2" t="n">
-        <v>7187968</v>
+        <v>7187993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120165973</v>
+        <v>120159863</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660916</v>
+        <v>661167</v>
       </c>
       <c r="R3" t="n">
-        <v>7187993</v>
+        <v>7188060</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120165974</v>
+        <v>120165975</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R4" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120159863</v>
+        <v>120165973</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>79636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R5" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120165974</v>
+        <v>120159863</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660916</v>
+        <v>661167</v>
       </c>
       <c r="R2" t="n">
-        <v>7187993</v>
+        <v>7188060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159863</v>
+        <v>120165973</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R3" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120165975</v>
+        <v>120165974</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661173</v>
+        <v>660916</v>
       </c>
       <c r="R4" t="n">
-        <v>7187968</v>
+        <v>7187993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120165973</v>
+        <v>120165975</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R5" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120165973</v>
+        <v>120165975</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R3" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120165975</v>
+        <v>120165973</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661173</v>
+        <v>660916</v>
       </c>
       <c r="R5" t="n">
-        <v>7187968</v>
+        <v>7187993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120159863</v>
+        <v>120165974</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R2" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120165975</v>
+        <v>120165973</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661173</v>
+        <v>660916</v>
       </c>
       <c r="R3" t="n">
-        <v>7187968</v>
+        <v>7187993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120165974</v>
+        <v>120165975</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R4" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120165973</v>
+        <v>120159863</v>
       </c>
       <c r="B5" t="n">
-        <v>79652</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660916</v>
+        <v>661167</v>
       </c>
       <c r="R5" t="n">
-        <v>7187993</v>
+        <v>7188060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120165974</v>
+        <v>120165975</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R2" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120165973</v>
+        <v>120159863</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660916</v>
+        <v>661167</v>
       </c>
       <c r="R3" t="n">
-        <v>7187993</v>
+        <v>7188060</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120165975</v>
+        <v>120165973</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661173</v>
+        <v>660916</v>
       </c>
       <c r="R4" t="n">
-        <v>7187968</v>
+        <v>7187993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120159863</v>
+        <v>120165974</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R5" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120165975</v>
+        <v>120159863</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661173</v>
+        <v>661167</v>
       </c>
       <c r="R2" t="n">
-        <v>7187968</v>
+        <v>7188060</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120159863</v>
+        <v>120165973</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R3" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120165973</v>
+        <v>120165974</v>
       </c>
       <c r="B4" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120165974</v>
+        <v>120165975</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R5" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 26961-2024 artfynd.xlsx
+++ b/artfynd/A 26961-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120159863</v>
+        <v>120165974</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661167</v>
+        <v>660916</v>
       </c>
       <c r="R2" t="n">
-        <v>7188060</v>
+        <v>7187993</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120165973</v>
+        <v>120165975</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660916</v>
+        <v>661173</v>
       </c>
       <c r="R3" t="n">
-        <v>7187993</v>
+        <v>7187968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120165974</v>
+        <v>120165973</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120165975</v>
+        <v>120159863</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661173</v>
+        <v>661167</v>
       </c>
       <c r="R5" t="n">
-        <v>7187968</v>
+        <v>7188060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
